--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260903.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260903.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.63%</t>
+          <t>9.79%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.47%</t>
+          <t>9.45%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.47%</t>
+          <t>6.70%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>6.02%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>4.10%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.90%</t>
+          <t>3.94%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.74%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.51%</t>
         </is>
       </c>
     </row>
@@ -792,161 +792,161 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>64,742,000</t>
+          <t>449,396,250</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>449,396,250</t>
+          <t>132,826,945</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>132,826,945</t>
+          <t>64,742,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>1,963</t>
+          <t>354,020,964</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>32,456,000</t>
+          <t>1,924</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>354,020,964</t>
+          <t>32,456,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>26,729,000</t>
+          <t>233,108,056</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
@@ -968,29 +968,29 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>233,108,056</t>
+          <t>26,729,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1012,24 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>196,411,000</t>
+          <t>145,204,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,22 +1041,22 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>29,496,000</t>
+          <t>196,411,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
@@ -1078,29 +1078,29 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>145,204,000</t>
+          <t>29,496,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -1166,73 +1166,73 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>53,388,000</t>
+          <t>254,199,845</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>254,199,845</t>
+          <t>272,189,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>272,189,000</t>
+          <t>53,388,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>31,598,741,347</t>
+          <t>31,592,953,146</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>5,184,742,226</t>
+          <t>5,048,828,934</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr"/>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>-607,144,928</t>
+          <t>-876,124,258</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr"/>
